--- a/files/港岛-渣甸山及黄泥涌峡-峻誉．渣甸山.xlsx
+++ b/files/港岛-渣甸山及黄泥涌峡-峻誉．渣甸山.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座 销控表" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -112,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -177,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,48 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -806,7 +669,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -852,7 +715,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -898,7 +761,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -994,7 +857,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1090,7 +953,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1136,7 +999,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1182,7 +1045,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1228,7 +1091,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1274,7 +1137,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1320,7 +1183,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1366,7 +1229,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1412,7 +1275,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1608,7 +1471,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1854,7 +1717,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1900,7 +1763,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -1946,7 +1809,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2038,7 +1901,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2084,7 +1947,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2626,7 +2489,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2672,7 +2535,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -2718,7 +2581,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -2764,7 +2627,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -2810,7 +2673,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -2856,7 +2719,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -2952,7 +2815,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -2998,7 +2861,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3044,7 +2907,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3090,7 +2953,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3136,7 +2999,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3182,7 +3045,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -3228,7 +3091,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -3274,7 +3137,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -3320,7 +3183,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -3366,7 +3229,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3462,7 +3325,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3558,7 +3421,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3604,7 +3467,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -3700,7 +3563,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -3796,7 +3659,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4042,7 +3905,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -6138,7 +6001,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -6210,1420 +6073,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>峻誉．渣甸山 - 1座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>34 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>19 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>5 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>10 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 2949呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 2841呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 1679呎 (4+房)
-$9,800万
-$58,368/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 1684呎 (4+房)
-$9,730万
-$57,779/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>A | 1679呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 1684呎 (4+房)
-$9,900万
-$58,789/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>A | 1679呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 1684呎 (4+房)
-$9,900万
-$58,789/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 1679呎 (4+房)
-$9,800万
-$58,368/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 1684呎 (4+房)
-$9,750万
-$57,898/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 1679呎 (4+房)
-$9,200万
-$54,795/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 1684呎 (4+房)
-$9,120万
-$54,157/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 1679呎 (4+房)
-$8,642万
-$51,471/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 1684呎 (4+房)
-$8,642万
-$51,318/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 1679呎 (4+房)
-$8,478万
-$50,494/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 1684呎 (4+房)
-$8,478万
-$50,344/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>A | 1679呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>B | 1686呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 1679呎 (4+房)
-$8,305万
-$49,464/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>B | 1686呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 1679呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 1686呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 1679呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 1686呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 1679呎 (4+房)
-$7,960万
-$47,409/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 1686呎 (4+房)
-$7,960万
-$47,212/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 1679呎 (4+房)
-$8,280万
-$49,315/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 1686呎 (4+房)
-$7,860万
-$46,619/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 1679呎 (4+房)
-$8,120万
-$48,362/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 1686呎 (4+房)
-$7,860万
-$46,619/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 1679呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 1686呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 1616呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 1686呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>峻誉．渣甸山 - 2座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>80 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>24 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>29 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>27 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 2595呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr"/>
-      <c r="E6" s="17" t="inlineStr"/>
-      <c r="F6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 2578呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr"/>
-      <c r="D7" s="17" t="inlineStr"/>
-      <c r="E7" s="17" t="inlineStr"/>
-      <c r="F7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 687呎 (2房)
-$2,714万
-$39,500/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 645呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 710呎 (2房)
-$3,300万
-$46,479/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 434呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>E | 439呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 687呎 (2房)
-$2,670万
-$38,865/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 645呎 (2房)
-$2,489万
-$38,589/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 710呎 (2房)
-$2,750万
-$38,732/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 434呎 (2房)
-$2,050万
-$47,235/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>E | 439呎 (2房)
-$2,041万
-$46,492/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 687呎 (2房)
-$2,638万
-$38,400/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 645呎 (2房)
-$2,454万
-$38,043/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>C | 710呎 (2房)
-$2,700万
-$38,028/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 434呎 (2房)
-$2,050万
-$47,235/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>E | 439呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 687呎 (2房)
-$2,615万
-$38,065/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 645呎 (2房)
-$2,436万
-$37,775/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 710呎 (2房)
-$2,682万
-$37,778/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 434呎 (2房)
-$1,988万
-$45,810/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>E | 439呎 (2房)
-$2,047万
-$46,622/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 687呎 (2房)
-$2,563万
-$37,300/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 645呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 710呎 (2房)
-$2,640万
-$37,180/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>D | 434呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>E | 439呎 (2房)
-$2,030万
-$46,241/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 687呎 (2房)
-$3,010万
-$43,814/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 645呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 710呎 (2房)
-$2,980万
-$41,972/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>D | 434呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>E | 439呎 (2房)
-$2,319万
-$52,832/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 687呎 (2房)
-$2,961万
-$43,100/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 645呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 710呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>D | 434呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>E | 439呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 687呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 645呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 711呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>E | 435呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 687呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 645呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 711呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>E | 435呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>A | 687呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="inlineStr">
-        <is>
-          <t>B | 645呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D17" s="19" t="inlineStr">
-        <is>
-          <t>C | 711呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E17" s="19" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F17" s="19" t="inlineStr">
-        <is>
-          <t>E | 435呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>A | 687呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C18" s="19" t="inlineStr">
-        <is>
-          <t>B | 645呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D18" s="19" t="inlineStr">
-        <is>
-          <t>C | 711呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E18" s="19" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F18" s="19" t="inlineStr">
-        <is>
-          <t>E | 435呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>A | 687呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="inlineStr">
-        <is>
-          <t>B | 645呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t>C | 711呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E19" s="19" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F19" s="19" t="inlineStr">
-        <is>
-          <t>E | 435呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>A | 687呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="inlineStr">
-        <is>
-          <t>B | 645呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>C | 711呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E20" s="19" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F20" s="19" t="inlineStr">
-        <is>
-          <t>E | 435呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>A | 687呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="inlineStr">
-        <is>
-          <t>B | 645呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D21" s="19" t="inlineStr">
-        <is>
-          <t>C | 711呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E21" s="19" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F21" s="19" t="inlineStr">
-        <is>
-          <t>E | 435呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>A | 690呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C22" s="19" t="inlineStr">
-        <is>
-          <t>B | 645呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D22" s="19" t="inlineStr">
-        <is>
-          <t>C | 711呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E22" s="19" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr"/>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 731呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 622呎 (2房)
-$2,288万
-$36,785/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>C | 686呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>D | 435呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-渣甸山及黄泥涌峡-峻誉．渣甸山.xlsx
+++ b/files/港岛-渣甸山及黄泥涌峡-峻誉．渣甸山.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +43,96 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +143,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +224,60 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +654,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -6073,4 +6253,1420 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 2949呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2841呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 1679呎 (4+房)
+$9800万
+$58,368/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 1684呎 (4+房)
+$9730万
+$57,779/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>A | 1679呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 1684呎 (4+房)
+$9900万
+$58,789/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>A | 1679呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 1684呎 (4+房)
+$9900万
+$58,789/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 1679呎 (4+房)
+$9800万
+$58,368/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 1684呎 (4+房)
+$9750万
+$57,898/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 1679呎 (4+房)
+$9200万
+$54,795/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 1684呎 (4+房)
+$9120万
+$54,157/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 1679呎 (4+房)
+$8642万
+$51,471/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 1684呎 (4+房)
+$8642万
+$51,318/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 1679呎 (4+房)
+$8478万
+$50,494/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 1684呎 (4+房)
+$8478万
+$50,344/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>A | 1679呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>B | 1686呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 1679呎 (4+房)
+$8305万
+$49,464/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>B | 1686呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 1679呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 1686呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 1679呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 1686呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 1679呎 (4+房)
+$7960万
+$47,409/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 1686呎 (4+房)
+$7960万
+$47,212/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 1679呎 (4+房)
+$8280万
+$49,315/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 1686呎 (4+房)
+$7860万
+$46,619/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 1679呎 (4+房)
+$8120万
+$48,362/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 1686呎 (4+房)
+$7860万
+$46,619/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 1679呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 1686呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 1616呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 1686呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 2595呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2578呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 687呎 (2房)
+$2714万
+$39,500/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 645呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 710呎 (2房)
+$3300万
+$46,479/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 434呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 439呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 687呎 (2房)
+$2670万
+$38,865/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 645呎 (2房)
+$2489万
+$38,589/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 710呎 (2房)
+$2750万
+$38,732/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 434呎 (2房)
+$2050万
+$47,235/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>E | 439呎 (2房)
+$2041万
+$46,492/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 687呎 (2房)
+$2638万
+$38,400/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 645呎 (2房)
+$2454万
+$38,043/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 710呎 (2房)
+$2700万
+$38,028/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 434呎 (2房)
+$2050万
+$47,235/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 439呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 687呎 (2房)
+$2615万
+$38,065/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 645呎 (2房)
+$2436万
+$37,775/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 710呎 (2房)
+$2682万
+$37,778/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 434呎 (2房)
+$1988万
+$45,810/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>E | 439呎 (2房)
+$2047万
+$46,622/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 687呎 (2房)
+$2563万
+$37,300/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 645呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 710呎 (2房)
+$2640万
+$37,180/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 434呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>E | 439呎 (2房)
+$2030万
+$46,241/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 687呎 (2房)
+$3010万
+$43,814/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 645呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 710呎 (2房)
+$2980万
+$41,972/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 434呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 439呎 (2房)
+$2319万
+$52,832/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 687呎 (2房)
+$2961万
+$43,100/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 645呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 710呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 434呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 439呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 687呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 645呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 711呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 435呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 687呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 645呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 711呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 435呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>A | 687呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>B | 645呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>C | 711呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>E | 435呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>A | 687呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>B | 645呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>C | 711呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>E | 435呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>A | 687呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>B | 645呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>C | 711呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>E | 435呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>A | 687呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>B | 645呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>C | 711呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>E | 435呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>A | 687呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>B | 645呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>C | 711呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>E | 435呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>A | 690呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>B | 645呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>C | 711呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr"/>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 731呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 622呎 (2房)
+$2288万
+$36,785/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 686呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 435呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-渣甸山及黄泥涌峡-峻誉．渣甸山.xlsx
+++ b/files/港岛-渣甸山及黄泥涌峡-峻誉．渣甸山.xlsx
@@ -654,7 +654,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-渣甸山及黄泥涌峡-峻誉．渣甸山.xlsx
+++ b/files/港岛-渣甸山及黄泥涌峡-峻誉．渣甸山.xlsx
@@ -644,7 +644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J116"/>
+  <dimension ref="A1:N116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -657,6 +657,10 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -714,6 +718,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -764,6 +788,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -814,6 +858,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -860,6 +924,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -906,6 +990,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -952,6 +1056,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1002,6 +1126,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1048,6 +1192,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1098,6 +1262,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1144,6 +1328,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1190,6 +1394,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1236,6 +1460,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1282,6 +1526,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1328,6 +1592,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1374,6 +1658,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1420,6 +1724,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1466,6 +1790,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1516,6 +1860,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1566,6 +1930,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1616,6 +2000,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1662,6 +2066,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1712,6 +2136,26 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1762,6 +2206,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1812,6 +2276,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1862,6 +2346,26 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1908,6 +2412,26 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1954,6 +2478,26 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2000,6 +2544,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2046,6 +2610,26 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2092,6 +2676,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2138,6 +2742,26 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2188,6 +2812,26 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2238,6 +2882,26 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2288,6 +2952,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2338,6 +3022,26 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2388,6 +3092,26 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2438,6 +3162,26 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2488,6 +3232,26 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2538,6 +3302,26 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2584,6 +3368,26 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2634,6 +3438,26 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2680,6 +3504,26 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2726,6 +3570,26 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2772,6 +3636,26 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2818,6 +3702,26 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2864,6 +3768,26 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2910,6 +3834,26 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2960,6 +3904,26 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3006,6 +3970,26 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3052,6 +4036,26 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3098,6 +4102,26 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3144,6 +4168,26 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3190,6 +4234,26 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3236,6 +4300,26 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3282,6 +4366,26 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3328,6 +4432,26 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3374,6 +4498,26 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3420,6 +4564,26 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3470,6 +4634,26 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3516,6 +4700,26 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3566,6 +4770,26 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3612,6 +4836,26 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3658,6 +4902,26 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3708,6 +4972,26 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3754,6 +5038,26 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3804,6 +5108,26 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3850,6 +5174,26 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3900,6 +5244,26 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3950,6 +5314,26 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4000,6 +5384,26 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4050,6 +5454,26 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4096,6 +5520,26 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4146,6 +5590,26 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4196,6 +5660,26 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4246,6 +5730,26 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4296,6 +5800,26 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4346,6 +5870,26 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4396,6 +5940,26 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4446,6 +6010,26 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4496,6 +6080,26 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4546,6 +6150,26 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4596,6 +6220,26 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4646,6 +6290,26 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4696,6 +6360,26 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4746,6 +6430,26 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4796,6 +6500,26 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L87" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4846,6 +6570,26 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4896,6 +6640,26 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L89" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4946,6 +6710,26 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4996,6 +6780,26 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5046,6 +6850,26 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L92" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5096,6 +6920,26 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L93" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5146,6 +6990,26 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5196,6 +7060,26 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L95" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5246,6 +7130,26 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L96" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5296,6 +7200,26 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L97" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5346,6 +7270,26 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L98" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5396,6 +7340,26 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5446,6 +7410,26 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5496,6 +7480,26 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5546,6 +7550,26 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5596,6 +7620,26 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5646,6 +7690,26 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5696,6 +7760,26 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5746,6 +7830,26 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5796,6 +7900,26 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L107" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5846,6 +7970,26 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L108" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5896,6 +8040,26 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L109" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5946,6 +8110,26 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L110" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5996,6 +8180,26 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L111" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6046,6 +8250,26 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L112" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6096,6 +8320,26 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L113" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6146,6 +8390,26 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L114" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6192,6 +8456,26 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L115" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6242,13 +8526,33 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L116" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -6400,7 +8704,7 @@
           <t>A | 1679呎 (4+房)
 $9800万
 $58,368/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -6408,7 +8712,7 @@
           <t>B | 1684呎 (4+房)
 $9730万
 $57,779/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
     </row>
@@ -6431,7 +8735,7 @@
           <t>B | 1684呎 (4+房)
 $9900万
 $58,789/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -6454,7 +8758,7 @@
           <t>B | 1684呎 (4+房)
 $9900万
 $58,789/呎
-(26年-06月)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
     </row>
@@ -6469,7 +8773,7 @@
           <t>A | 1679呎 (4+房)
 $9800万
 $58,368/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -6477,7 +8781,7 @@
           <t>B | 1684呎 (4+房)
 $9750万
 $57,898/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
     </row>
@@ -6492,7 +8796,7 @@
           <t>A | 1679呎 (4+房)
 $9200万
 $54,795/呎
-(26年-06月)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -6500,7 +8804,7 @@
           <t>B | 1684呎 (4+房)
 $9120万
 $54,157/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
     </row>
@@ -6515,7 +8819,7 @@
           <t>A | 1679呎 (4+房)
 $8642万
 $51,471/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -6523,7 +8827,7 @@
           <t>B | 1684呎 (4+房)
 $8642万
 $51,318/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
     </row>
@@ -6538,7 +8842,7 @@
           <t>A | 1679呎 (4+房)
 $8478万
 $50,494/呎
-(26年-06月)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -6546,7 +8850,7 @@
           <t>B | 1684呎 (4+房)
 $8478万
 $50,344/呎
-(26年-06月)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
     </row>
@@ -6584,7 +8888,7 @@
           <t>A | 1679呎 (4+房)
 $8305万
 $49,464/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -6653,7 +8957,7 @@
           <t>A | 1679呎 (4+房)
 $7960万
 $47,409/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -6661,7 +8965,7 @@
           <t>B | 1686呎 (4+房)
 $7960万
 $47,212/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -6676,7 +8980,7 @@
           <t>A | 1679呎 (4+房)
 $8280万
 $49,315/呎
-(26年-06月)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -6684,7 +8988,7 @@
           <t>B | 1686呎 (4+房)
 $7860万
 $46,619/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
     </row>
@@ -6699,7 +9003,7 @@
           <t>A | 1679呎 (4+房)
 $8120万
 $48,362/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -6707,7 +9011,7 @@
           <t>B | 1686呎 (4+房)
 $7860万
 $46,619/呎
-(26年-06月)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
     </row>
@@ -6935,7 +9239,7 @@
           <t>A | 687呎 (2房)
 $2714万
 $39,500/呎
-(25年-09月)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -6951,7 +9255,7 @@
           <t>C | 710呎 (2房)
 $3300万
 $46,479/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -6982,7 +9286,7 @@
           <t>A | 687呎 (2房)
 $2670万
 $38,865/呎
-(25年-11月)</t>
+(25年-11月-16日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -6990,7 +9294,7 @@
           <t>B | 645呎 (2房)
 $2489万
 $38,589/呎
-(25年-11月)</t>
+(25年-11月-16日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -6998,7 +9302,7 @@
           <t>C | 710呎 (2房)
 $2750万
 $38,732/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -7006,7 +9310,7 @@
           <t>D | 434呎 (2房)
 $2050万
 $47,235/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -7014,7 +9318,7 @@
           <t>E | 439呎 (2房)
 $2041万
 $46,492/呎
-(25年-11月)</t>
+(25年-11月-16日)</t>
         </is>
       </c>
     </row>
@@ -7029,7 +9333,7 @@
           <t>A | 687呎 (2房)
 $2638万
 $38,400/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -7037,7 +9341,7 @@
           <t>B | 645呎 (2房)
 $2454万
 $38,043/呎
-(25年-07月)</t>
+(25年-07月-16日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -7045,7 +9349,7 @@
           <t>C | 710呎 (2房)
 $2700万
 $38,028/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -7053,7 +9357,7 @@
           <t>D | 434呎 (2房)
 $2050万
 $47,235/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -7076,7 +9380,7 @@
           <t>A | 687呎 (2房)
 $2615万
 $38,065/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -7084,7 +9388,7 @@
           <t>B | 645呎 (2房)
 $2436万
 $37,775/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -7092,7 +9396,7 @@
           <t>C | 710呎 (2房)
 $2682万
 $37,778/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -7100,7 +9404,7 @@
           <t>D | 434呎 (2房)
 $1988万
 $45,810/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -7108,7 +9412,7 @@
           <t>E | 439呎 (2房)
 $2047万
 $46,622/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
     </row>
@@ -7123,7 +9427,7 @@
           <t>A | 687呎 (2房)
 $2563万
 $37,300/呎
-(25年-08月)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -7139,7 +9443,7 @@
           <t>C | 710呎 (2房)
 $2640万
 $37,180/呎
-(25年-08月)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -7155,7 +9459,7 @@
           <t>E | 439呎 (2房)
 $2030万
 $46,241/呎
-(25年-08月)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
     </row>
@@ -7170,7 +9474,7 @@
           <t>A | 687呎 (2房)
 $3010万
 $43,814/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -7186,7 +9490,7 @@
           <t>C | 710呎 (2房)
 $2980万
 $41,972/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -7202,7 +9506,7 @@
           <t>E | 439呎 (2房)
 $2319万
 $52,832/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
     </row>
@@ -7217,7 +9521,7 @@
           <t>A | 687呎 (2房)
 $2961万
 $43,100/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -7641,7 +9945,7 @@
           <t>B | 622呎 (2房)
 $2288万
 $36,785/呎
-(26年-01月)</t>
+(26年-01月-18日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">

--- a/files/港岛-渣甸山及黄泥涌峡-峻誉．渣甸山.xlsx
+++ b/files/港岛-渣甸山及黄泥涌峡-峻誉．渣甸山.xlsx
@@ -2599,7 +2599,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -8980,7 +8980,7 @@
           <t>A | 1679呎 (4+房)
 $8280万
 $49,315/呎
-(26年-06月-14日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">

--- a/files/港岛-渣甸山及黄泥涌峡-峻誉．渣甸山.xlsx
+++ b/files/港岛-渣甸山及黄泥涌峡-峻誉．渣甸山.xlsx
@@ -8704,7 +8704,7 @@
           <t>A | 1679呎 (4+房)
 $9800万
 $58,368/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -8712,7 +8712,7 @@
           <t>B | 1684呎 (4+房)
 $9730万
 $57,779/呎
-(26年-05月-14日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
           <t>B | 1684呎 (4+房)
 $9900万
 $58,789/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -8758,7 +8758,7 @@
           <t>B | 1684呎 (4+房)
 $9900万
 $58,789/呎
-(26年-06月-15日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -8773,7 +8773,7 @@
           <t>A | 1679呎 (4+房)
 $9800万
 $58,368/呎
-(26年-06月-17日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -8781,7 +8781,7 @@
           <t>B | 1684呎 (4+房)
 $9750万
 $57,898/呎
-(26年-06月-17日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -8796,7 +8796,7 @@
           <t>A | 1679呎 (4+房)
 $9200万
 $54,795/呎
-(26年-06月-22日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -8804,7 +8804,7 @@
           <t>B | 1684呎 (4+房)
 $9120万
 $54,157/呎
-(26年-06月-24日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -8819,7 +8819,7 @@
           <t>A | 1679呎 (4+房)
 $8642万
 $51,471/呎
-(26年-06月-28日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -8827,7 +8827,7 @@
           <t>B | 1684呎 (4+房)
 $8642万
 $51,318/呎
-(26年-06月-28日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
           <t>A | 1679呎 (4+房)
 $8478万
 $50,494/呎
-(26年-06月-22日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -8850,7 +8850,7 @@
           <t>B | 1684呎 (4+房)
 $8478万
 $50,344/呎
-(26年-06月-22日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -8888,7 +8888,7 @@
           <t>A | 1679呎 (4+房)
 $8305万
 $49,464/呎
-(26年-06月-28日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -8957,7 +8957,7 @@
           <t>A | 1679呎 (4+房)
 $7960万
 $47,409/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -8965,7 +8965,7 @@
           <t>B | 1686呎 (4+房)
 $7960万
 $47,212/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
           <t>A | 1679呎 (4+房)
 $8280万
 $49,315/呎
-(26年-07月-14日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -8988,7 +8988,7 @@
           <t>B | 1686呎 (4+房)
 $7860万
 $46,619/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -9003,7 +9003,7 @@
           <t>A | 1679呎 (4+房)
 $8120万
 $48,362/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -9011,7 +9011,7 @@
           <t>B | 1686呎 (4+房)
 $7860万
 $46,619/呎
-(26年-06月-23日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -9239,7 +9239,7 @@
           <t>A | 687呎 (2房)
 $2714万
 $39,500/呎
-(25年-09月-15日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -9255,7 +9255,7 @@
           <t>C | 710呎 (2房)
 $3300万
 $46,479/呎
-(26年-07月-02日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -9286,7 +9286,7 @@
           <t>A | 687呎 (2房)
 $2670万
 $38,865/呎
-(25年-11月-16日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -9294,7 +9294,7 @@
           <t>B | 645呎 (2房)
 $2489万
 $38,589/呎
-(25年-11月-16日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -9302,7 +9302,7 @@
           <t>C | 710呎 (2房)
 $2750万
 $38,732/呎
-(25年-12月-17日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -9310,7 +9310,7 @@
           <t>D | 434呎 (2房)
 $2050万
 $47,235/呎
-(25年-12月-18日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -9318,7 +9318,7 @@
           <t>E | 439呎 (2房)
 $2041万
 $46,492/呎
-(25年-11月-16日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -9333,7 +9333,7 @@
           <t>A | 687呎 (2房)
 $2638万
 $38,400/呎
-(25年-07月-03日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -9341,7 +9341,7 @@
           <t>B | 645呎 (2房)
 $2454万
 $38,043/呎
-(25年-07月-16日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -9349,7 +9349,7 @@
           <t>C | 710呎 (2房)
 $2700万
 $38,028/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -9357,7 +9357,7 @@
           <t>D | 434呎 (2房)
 $2050万
 $47,235/呎
-(25年-07月-13日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -9380,7 +9380,7 @@
           <t>A | 687呎 (2房)
 $2615万
 $38,065/呎
-(25年-12月-08日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -9388,7 +9388,7 @@
           <t>B | 645呎 (2房)
 $2436万
 $37,775/呎
-(25年-12月-08日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -9396,7 +9396,7 @@
           <t>C | 710呎 (2房)
 $2682万
 $37,778/呎
-(25年-12月-08日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -9404,7 +9404,7 @@
           <t>D | 434呎 (2房)
 $1988万
 $45,810/呎
-(25年-12月-08日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -9412,7 +9412,7 @@
           <t>E | 439呎 (2房)
 $2047万
 $46,622/呎
-(25年-12月-08日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -9427,7 +9427,7 @@
           <t>A | 687呎 (2房)
 $2563万
 $37,300/呎
-(25年-08月-11日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -9443,7 +9443,7 @@
           <t>C | 710呎 (2房)
 $2640万
 $37,180/呎
-(25年-08月-28日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -9459,7 +9459,7 @@
           <t>E | 439呎 (2房)
 $2030万
 $46,241/呎
-(25年-08月-11日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -9474,7 +9474,7 @@
           <t>A | 687呎 (2房)
 $3010万
 $43,814/呎
-(26年-06月-29日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -9490,7 +9490,7 @@
           <t>C | 710呎 (2房)
 $2980万
 $41,972/呎
-(26年-06月-17日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -9506,7 +9506,7 @@
           <t>E | 439呎 (2房)
 $2319万
 $52,832/呎
-(26年-06月-29日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -9521,7 +9521,7 @@
           <t>A | 687呎 (2房)
 $2961万
 $43,100/呎
-(26年-06月-25日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -9945,7 +9945,7 @@
           <t>B | 622呎 (2房)
 $2288万
 $36,785/呎
-(26年-01月-18日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">

--- a/files/港岛-渣甸山及黄泥涌峡-峻誉．渣甸山.xlsx
+++ b/files/港岛-渣甸山及黄泥涌峡-峻誉．渣甸山.xlsx
@@ -8704,7 +8704,7 @@
           <t>A | 1679呎 (4+房)
 $9800万
 $58,368/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -8712,7 +8712,7 @@
           <t>B | 1684呎 (4+房)
 $9730万
 $57,779/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
           <t>B | 1684呎 (4+房)
 $9900万
 $58,789/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -8758,7 +8758,7 @@
           <t>B | 1684呎 (4+房)
 $9900万
 $58,789/呎
-(26年-06月)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
     </row>
@@ -8773,7 +8773,7 @@
           <t>A | 1679呎 (4+房)
 $9800万
 $58,368/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -8781,7 +8781,7 @@
           <t>B | 1684呎 (4+房)
 $9750万
 $57,898/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
     </row>
@@ -8796,7 +8796,7 @@
           <t>A | 1679呎 (4+房)
 $9200万
 $54,795/呎
-(26年-06月)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -8804,7 +8804,7 @@
           <t>B | 1684呎 (4+房)
 $9120万
 $54,157/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
     </row>
@@ -8819,7 +8819,7 @@
           <t>A | 1679呎 (4+房)
 $8642万
 $51,471/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -8827,7 +8827,7 @@
           <t>B | 1684呎 (4+房)
 $8642万
 $51,318/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
           <t>A | 1679呎 (4+房)
 $8478万
 $50,494/呎
-(26年-06月)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -8850,7 +8850,7 @@
           <t>B | 1684呎 (4+房)
 $8478万
 $50,344/呎
-(26年-06月)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
     </row>
@@ -8888,7 +8888,7 @@
           <t>A | 1679呎 (4+房)
 $8305万
 $49,464/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -8957,7 +8957,7 @@
           <t>A | 1679呎 (4+房)
 $7960万
 $47,409/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -8965,7 +8965,7 @@
           <t>B | 1686呎 (4+房)
 $7960万
 $47,212/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
           <t>A | 1679呎 (4+房)
 $8280万
 $49,315/呎
-(26年-07月)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -8988,7 +8988,7 @@
           <t>B | 1686呎 (4+房)
 $7860万
 $46,619/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
     </row>
@@ -9003,7 +9003,7 @@
           <t>A | 1679呎 (4+房)
 $8120万
 $48,362/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -9011,7 +9011,7 @@
           <t>B | 1686呎 (4+房)
 $7860万
 $46,619/呎
-(26年-06月)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
     </row>
@@ -9239,7 +9239,7 @@
           <t>A | 687呎 (2房)
 $2714万
 $39,500/呎
-(25年-09月)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -9255,7 +9255,7 @@
           <t>C | 710呎 (2房)
 $3300万
 $46,479/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -9286,7 +9286,7 @@
           <t>A | 687呎 (2房)
 $2670万
 $38,865/呎
-(25年-11月)</t>
+(25年-11月-16日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -9294,7 +9294,7 @@
           <t>B | 645呎 (2房)
 $2489万
 $38,589/呎
-(25年-11月)</t>
+(25年-11月-16日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -9302,7 +9302,7 @@
           <t>C | 710呎 (2房)
 $2750万
 $38,732/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -9310,7 +9310,7 @@
           <t>D | 434呎 (2房)
 $2050万
 $47,235/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -9318,7 +9318,7 @@
           <t>E | 439呎 (2房)
 $2041万
 $46,492/呎
-(25年-11月)</t>
+(25年-11月-16日)</t>
         </is>
       </c>
     </row>
@@ -9333,7 +9333,7 @@
           <t>A | 687呎 (2房)
 $2638万
 $38,400/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -9341,7 +9341,7 @@
           <t>B | 645呎 (2房)
 $2454万
 $38,043/呎
-(25年-07月)</t>
+(25年-07月-16日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -9349,7 +9349,7 @@
           <t>C | 710呎 (2房)
 $2700万
 $38,028/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -9357,7 +9357,7 @@
           <t>D | 434呎 (2房)
 $2050万
 $47,235/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -9380,7 +9380,7 @@
           <t>A | 687呎 (2房)
 $2615万
 $38,065/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -9388,7 +9388,7 @@
           <t>B | 645呎 (2房)
 $2436万
 $37,775/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -9396,7 +9396,7 @@
           <t>C | 710呎 (2房)
 $2682万
 $37,778/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -9404,7 +9404,7 @@
           <t>D | 434呎 (2房)
 $1988万
 $45,810/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -9412,7 +9412,7 @@
           <t>E | 439呎 (2房)
 $2047万
 $46,622/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
     </row>
@@ -9427,7 +9427,7 @@
           <t>A | 687呎 (2房)
 $2563万
 $37,300/呎
-(25年-08月)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -9443,7 +9443,7 @@
           <t>C | 710呎 (2房)
 $2640万
 $37,180/呎
-(25年-08月)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -9459,7 +9459,7 @@
           <t>E | 439呎 (2房)
 $2030万
 $46,241/呎
-(25年-08月)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
     </row>
@@ -9474,7 +9474,7 @@
           <t>A | 687呎 (2房)
 $3010万
 $43,814/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -9490,7 +9490,7 @@
           <t>C | 710呎 (2房)
 $2980万
 $41,972/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -9506,7 +9506,7 @@
           <t>E | 439呎 (2房)
 $2319万
 $52,832/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
     </row>
@@ -9521,7 +9521,7 @@
           <t>A | 687呎 (2房)
 $2961万
 $43,100/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -9945,7 +9945,7 @@
           <t>B | 622呎 (2房)
 $2288万
 $36,785/呎
-(26年-01月)</t>
+(26年-01月-18日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
